--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42094,6 +42094,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1815">
+      <c r="A1815" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1815" t="n">
+        <v>800</v>
+      </c>
+      <c r="C1815" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="D1815" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="E1815" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="F1815" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="G1815" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42117,6 +42117,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1816">
+      <c r="A1816" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1816" t="n">
+        <v>13600</v>
+      </c>
+      <c r="C1816" t="n">
+        <v>0.71399998664856</v>
+      </c>
+      <c r="D1816" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="F1816" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="G1816" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42140,6 +42140,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1817">
+      <c r="A1817" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1817" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C1817" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D1817" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="F1817" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="G1817" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42004,22 +42004,22 @@
     </row>
     <row r="1811">
       <c r="A1811" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1811" t="n">
-        <v>13600</v>
+        <v>12000</v>
       </c>
       <c r="C1811" t="n">
-        <v>0.722000002861023</v>
+        <v>0.71399998664856</v>
       </c>
       <c r="D1811" t="n">
-        <v>0.705999970436096</v>
+        <v>0.702000021934509</v>
       </c>
       <c r="E1811" t="n">
-        <v>0.717999994754791</v>
+        <v>0.702000021934509</v>
       </c>
       <c r="F1811" t="n">
-        <v>0.705999970436096</v>
+        <v>0.71399998664856</v>
       </c>
       <c r="G1811" t="s">
         <v>7</v>
@@ -42027,19 +42027,19 @@
     </row>
     <row r="1812">
       <c r="A1812" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1812" t="n">
-        <v>3200</v>
+        <v>13600</v>
       </c>
       <c r="C1812" t="n">
-        <v>0.705999970436096</v>
+        <v>0.722000002861023</v>
       </c>
       <c r="D1812" t="n">
         <v>0.705999970436096</v>
       </c>
       <c r="E1812" t="n">
-        <v>0.705999970436096</v>
+        <v>0.717999994754791</v>
       </c>
       <c r="F1812" t="n">
         <v>0.705999970436096</v>
@@ -42050,22 +42050,22 @@
     </row>
     <row r="1813">
       <c r="A1813" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1813" t="n">
-        <v>8000</v>
+        <v>3200</v>
       </c>
       <c r="C1813" t="n">
-        <v>0.709999978542328</v>
+        <v>0.705999970436096</v>
       </c>
       <c r="D1813" t="n">
-        <v>0.709999978542328</v>
+        <v>0.705999970436096</v>
       </c>
       <c r="E1813" t="n">
-        <v>0.709999978542328</v>
+        <v>0.705999970436096</v>
       </c>
       <c r="F1813" t="n">
-        <v>0.709999978542328</v>
+        <v>0.705999970436096</v>
       </c>
       <c r="G1813" t="s">
         <v>7</v>
@@ -42073,19 +42073,19 @@
     </row>
     <row r="1814">
       <c r="A1814" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1814" t="n">
-        <v>14400</v>
+        <v>8000</v>
       </c>
       <c r="C1814" t="n">
         <v>0.709999978542328</v>
       </c>
       <c r="D1814" t="n">
-        <v>0.694000005722046</v>
+        <v>0.709999978542328</v>
       </c>
       <c r="E1814" t="n">
-        <v>0.698000013828278</v>
+        <v>0.709999978542328</v>
       </c>
       <c r="F1814" t="n">
         <v>0.709999978542328</v>
@@ -42096,22 +42096,22 @@
     </row>
     <row r="1815">
       <c r="A1815" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1815" t="n">
-        <v>800</v>
+        <v>14400</v>
       </c>
       <c r="C1815" t="n">
-        <v>0.703999996185303</v>
+        <v>0.709999978542328</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.703999996185303</v>
+        <v>0.694000005722046</v>
       </c>
       <c r="E1815" t="n">
-        <v>0.703999996185303</v>
+        <v>0.698000013828278</v>
       </c>
       <c r="F1815" t="n">
-        <v>0.703999996185303</v>
+        <v>0.709999978542328</v>
       </c>
       <c r="G1815" t="s">
         <v>7</v>
@@ -42119,22 +42119,22 @@
     </row>
     <row r="1816">
       <c r="A1816" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1816" t="n">
-        <v>13600</v>
+        <v>800</v>
       </c>
       <c r="C1816" t="n">
-        <v>0.71399998664856</v>
+        <v>0.703999996185303</v>
       </c>
       <c r="D1816" t="n">
-        <v>0.695999979972839</v>
+        <v>0.703999996185303</v>
       </c>
       <c r="E1816" t="n">
-        <v>0.695999979972839</v>
+        <v>0.703999996185303</v>
       </c>
       <c r="F1816" t="n">
-        <v>0.698000013828278</v>
+        <v>0.703999996185303</v>
       </c>
       <c r="G1816" t="s">
         <v>7</v>
@@ -42142,24 +42142,70 @@
     </row>
     <row r="1817">
       <c r="A1817" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1817" t="n">
+        <v>13600</v>
+      </c>
+      <c r="C1817" t="n">
+        <v>0.71399998664856</v>
+      </c>
+      <c r="D1817" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="F1817" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="G1817" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B1817" t="n">
+      <c r="B1818" t="n">
         <v>2400</v>
       </c>
-      <c r="C1817" t="n">
+      <c r="C1818" t="n">
         <v>0.709999978542328</v>
       </c>
-      <c r="D1817" t="n">
+      <c r="D1818" t="n">
         <v>0.698000013828278</v>
       </c>
-      <c r="E1817" t="n">
+      <c r="E1818" t="n">
         <v>0.698000013828278</v>
       </c>
-      <c r="F1817" t="n">
+      <c r="F1818" t="n">
         <v>0.709999978542328</v>
       </c>
-      <c r="G1817" t="s">
+      <c r="G1818" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1819" t="n">
+        <v>40800</v>
+      </c>
+      <c r="C1819" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="D1819" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="E1819" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="F1819" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="G1819" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -47773,6 +47773,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1824">
+      <c r="A1824" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1824" t="n">
+        <v>32800</v>
+      </c>
+      <c r="C1824" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="D1824" t="n">
+        <v>0.691999971866608</v>
+      </c>
+      <c r="E1824" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="F1824" t="n">
+        <v>0.691999971866608</v>
+      </c>
+      <c r="G1824" t="n">
+        <v>0.691999971866608</v>
+      </c>
+      <c r="H1824" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -47799,6 +47799,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1825">
+      <c r="A1825" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1825" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C1825" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D1825" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="E1825" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="F1825" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="G1825" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="H1825" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -47877,6 +47877,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1828">
+      <c r="A1828" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1828" t="n">
+        <v>10400</v>
+      </c>
+      <c r="C1828" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="G1828" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="H1828" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42478,8 +42478,31 @@
       <c r="E1831" t="n">
         <v>0.801999986171722</v>
       </c>
-      <c r="F1831"/>
+      <c r="F1831" t="n">
+        <v>0.772000014781952</v>
+      </c>
       <c r="G1831" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1832" t="n">
+        <v>19200</v>
+      </c>
+      <c r="C1832" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>0.734000027179718</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="F1832"/>
+      <c r="G1832" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42501,8 +42501,31 @@
       <c r="E1832" t="n">
         <v>0.769999980926514</v>
       </c>
-      <c r="F1832"/>
+      <c r="F1832" t="n">
+        <v>0.748000025749207</v>
+      </c>
       <c r="G1832" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>19200</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>0.726000010967255</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>0.755999982357025</v>
+      </c>
+      <c r="F1833"/>
+      <c r="G1833" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42524,8 +42524,31 @@
       <c r="E1833" t="n">
         <v>0.755999982357025</v>
       </c>
-      <c r="F1833"/>
+      <c r="F1833" t="n">
+        <v>0.73199999332428</v>
+      </c>
       <c r="G1833" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1834" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C1834" t="n">
+        <v>0.723999977111816</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>0.705999970436096</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>0.723999977111816</v>
+      </c>
+      <c r="F1834"/>
+      <c r="G1834" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42547,8 +42547,31 @@
       <c r="E1834" t="n">
         <v>0.723999977111816</v>
       </c>
-      <c r="F1834"/>
+      <c r="F1834" t="n">
+        <v>0.705999970436096</v>
+      </c>
       <c r="G1834" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1835" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1835" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>0.708000004291534</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="F1835"/>
+      <c r="G1835" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42577,6 +42577,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1836">
+      <c r="A1836" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1836" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="G1836" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -42600,6 +42600,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1837">
+      <c r="A1837" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>0.705999970436096</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>0.705999970436096</v>
+      </c>
+      <c r="G1837" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -48189,6 +48189,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1840">
+      <c r="A1840" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1840" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>0.681999981403351</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="H1840" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -53767,6 +53767,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1842">
+      <c r="A1842" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1842" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="H1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1842" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1843" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="H1843" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I1843" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -53825,6 +53825,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1844">
+      <c r="A1844" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1844" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>0.685999989509583</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>0.685999989509583</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>0.681999981403351</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>0.681999981403351</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>0.681999981403351</v>
+      </c>
+      <c r="H1844" t="n">
+        <v>6400</v>
+      </c>
+      <c r="I1844" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -53854,6 +53854,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1845">
+      <c r="A1845" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1845" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1845" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>0.674000024795532</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>0.674000024795532</v>
+      </c>
+      <c r="H1845" t="n">
+        <v>43200</v>
+      </c>
+      <c r="I1845" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -53883,6 +53883,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1846">
+      <c r="A1846" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1846" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1846" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="H1846" t="n">
+        <v>10400</v>
+      </c>
+      <c r="I1846" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -53912,6 +53912,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1847">
+      <c r="A1847" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1847" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1847" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>0.663999974727631</v>
+      </c>
+      <c r="H1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1847" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1848" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="H1848" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I1848" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -53970,6 +53970,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1849">
+      <c r="A1849" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1849" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1849" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="D1849" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="G1849" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="H1849" t="n">
+        <v>10400</v>
+      </c>
+      <c r="I1849" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CBB.MI.xlsx
+++ b/data/CBB.MI.xlsx
@@ -53999,6 +53999,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1850">
+      <c r="A1850" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1850" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1850" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="D1850" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="G1850" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="H1850" t="n">
+        <v>800</v>
+      </c>
+      <c r="I1850" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
